--- a/2.WBS/xlsx/WBS_현대이지웰_최종프로젝트.xlsx
+++ b/2.WBS/xlsx/WBS_현대이지웰_최종프로젝트.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\GamesungCoding\ResourceRepo\2.WBS\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93F8EBD-CABE-466A-9AE6-B6609EA792D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6183F8F5-F349-451B-A1D6-07F81B03BB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="51">
   <si>
     <t>구분</t>
   </si>
@@ -214,12 +214,6 @@
   </si>
   <si>
     <t>기타 요구 제출물 확인</t>
-  </si>
-  <si>
-    <t>특강</t>
-  </si>
-  <si>
-    <t>MSA특강</t>
   </si>
   <si>
     <t>요구사항 분석 및 명세</t>
@@ -921,6 +915,15 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -930,27 +933,11 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -1197,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BO1001"/>
+  <dimension ref="A1:BO998"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" style="5" customWidth="1"/>
@@ -1832,7 +1819,7 @@
         <v>45952</v>
       </c>
       <c r="F5" s="11">
-        <f t="shared" ref="F5:F8" si="9">IF(AND(E5&lt;&gt;"", D5&lt;&gt;""), E5+D5-1, "")</f>
+        <f t="shared" ref="F5:F7" si="9">IF(AND(E5&lt;&gt;"", D5&lt;&gt;""), E5+D5-1, "")</f>
         <v>45952</v>
       </c>
       <c r="G5" s="36" t="str" cm="1">
@@ -1903,19 +1890,23 @@
     <row r="6" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="53"/>
       <c r="B6" s="18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="37">
         <v>1</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11" t="str">
+      <c r="D6" s="10">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11">
+        <v>45997</v>
+      </c>
+      <c r="F6" s="11">
         <f t="shared" si="9"/>
-        <v/>
+        <v>45997</v>
       </c>
       <c r="G6" s="36" t="str" cm="1">
-        <f t="array" ref="G6">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C4:I4="O", 담당자!C$2:I$2, ""))</f>
+        <f t="array" ref="G6">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C5:I5="O", 담당자!C$2:I$2, ""))</f>
         <v>안규태</v>
       </c>
       <c r="H6" s="12"/>
@@ -1982,19 +1973,23 @@
     <row r="7" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="53"/>
       <c r="B7" s="18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="37">
         <v>1</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11" t="str">
+      <c r="D7" s="10">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11">
+        <v>46010</v>
+      </c>
+      <c r="F7" s="11">
         <f t="shared" si="9"/>
-        <v/>
+        <v>46010</v>
       </c>
       <c r="G7" s="36" t="str" cm="1">
-        <f t="array" ref="G7">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C5:I5="O", 담당자!C$2:I$2, ""))</f>
+        <f t="array" ref="G7">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C6:I6="O", 담당자!C$2:I$2, ""))</f>
         <v>안규태</v>
       </c>
       <c r="H7" s="12"/>
@@ -2059,22 +2054,31 @@
       <c r="BO7" s="12"/>
     </row>
     <row r="8" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="53"/>
-      <c r="B8" s="18" t="s">
+      <c r="A8" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="37">
+        <f>IF(COUNTBLANK(C9:C11)=4, "", SUM(C9:C11)/COUNT(C9:C11))</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="10">
+        <f>IF(AND(F8&lt;&gt;"", E8&lt;&gt;""), F8-E8+1, "")</f>
         <v>11</v>
       </c>
-      <c r="C8" s="37">
-        <v>1</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11" t="str">
-        <f t="shared" si="9"/>
+      <c r="E8" s="11">
+        <f>IF(COUNTA(E9:E11)=0,"", MIN(E9:E11))</f>
+        <v>45951</v>
+      </c>
+      <c r="F8" s="11">
+        <f>IF(COUNTBLANK(F9:F11)=4,"", MAX(F9:F11))</f>
+        <v>45961</v>
+      </c>
+      <c r="G8" s="38" t="str" cm="1">
+        <f t="array" ref="G8">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C7:I7="O", 담당자!C$2:I$2, ""))</f>
         <v/>
-      </c>
-      <c r="G8" s="36" t="str" cm="1">
-        <f t="array" ref="G8">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C6:I6="O", 담당자!C$2:I$2, ""))</f>
-        <v>안규태</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
@@ -2138,31 +2142,26 @@
       <c r="BO8" s="12"/>
     </row>
     <row r="9" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="41" t="s">
-        <v>24</v>
+      <c r="A9" s="50"/>
+      <c r="B9" s="42" t="s">
+        <v>23</v>
       </c>
       <c r="C9" s="37">
-        <f>IF(COUNTBLANK(C10:C12)=4, "", SUM(C10:C12)/COUNT(C10:C12))</f>
         <v>1</v>
       </c>
       <c r="D9" s="10">
-        <f>IF(AND(F9&lt;&gt;"", E9&lt;&gt;""), F9-E9+1, "")</f>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E9" s="11">
-        <f>IF(COUNTA(E10:E12)=0,"", MIN(E10:E12))</f>
         <v>45951</v>
       </c>
       <c r="F9" s="11">
-        <f>IF(COUNTBLANK(F10:F12)=4,"", MAX(F10:F12))</f>
-        <v>45961</v>
-      </c>
-      <c r="G9" s="38" t="str" cm="1">
-        <f t="array" ref="G9">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C7:I7="O", 담당자!C$2:I$2, ""))</f>
-        <v/>
+        <f>IF(AND(E9&lt;&gt;"", D9&lt;&gt;""), E9+D9-1, "")</f>
+        <v>45954</v>
+      </c>
+      <c r="G9" s="36" t="str" cm="1">
+        <f t="array" ref="G9">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C8:I8="O", 담당자!C$2:I$2, ""))</f>
+        <v>팀 전체</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -2228,24 +2227,24 @@
     <row r="10" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="50"/>
       <c r="B10" s="42" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C10" s="37">
         <v>1</v>
       </c>
       <c r="D10" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" s="11">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="F10" s="11">
         <f>IF(AND(E10&lt;&gt;"", D10&lt;&gt;""), E10+D10-1, "")</f>
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="G10" s="36" t="str" cm="1">
-        <f t="array" ref="G10">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C8:I8="O", 담당자!C$2:I$2, ""))</f>
-        <v>팀 전체</v>
+        <f t="array" ref="G10">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C9:I9="O", 담당자!C$2:I$2, ""))</f>
+        <v>김수민, 신운용</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -2311,7 +2310,7 @@
     <row r="11" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="50"/>
       <c r="B11" s="42" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C11" s="37">
         <v>1</v>
@@ -2320,15 +2319,16 @@
         <v>2</v>
       </c>
       <c r="E11" s="11">
-        <v>45957</v>
+        <f>F10+2</f>
+        <v>45960</v>
       </c>
       <c r="F11" s="11">
-        <f>IF(AND(E11&lt;&gt;"", D11&lt;&gt;""), E11+D11-1, "")</f>
-        <v>45958</v>
+        <f t="shared" ref="F11:F29" si="10">IF(AND(E11&lt;&gt;"", D11&lt;&gt;""), E11+D11-1, "")</f>
+        <v>45961</v>
       </c>
       <c r="G11" s="36" t="str" cm="1">
-        <f t="array" ref="G11">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C9:I9="O", 담당자!C$2:I$2, ""))</f>
-        <v>김수민, 신운용</v>
+        <f t="array" ref="G11">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C10:I10="O", 담당자!C$2:I$2, ""))</f>
+        <v>안규태, 장지훈</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
@@ -2393,26 +2393,28 @@
     </row>
     <row r="12" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="50"/>
-      <c r="B12" s="42" t="s">
-        <v>52</v>
+      <c r="B12" s="41" t="s">
+        <v>28</v>
       </c>
       <c r="C12" s="37">
+        <f>IF(COUNTBLANK(C13:C16)=4, "", SUM(C13:C16)/COUNT(C13:C16))</f>
         <v>1</v>
       </c>
       <c r="D12" s="10">
-        <v>2</v>
+        <f>IF(AND(F12&lt;&gt;"", E12&lt;&gt;""), F12-E12+1, "")</f>
+        <v>15</v>
       </c>
       <c r="E12" s="11">
-        <f>F11+2</f>
-        <v>45960</v>
+        <f>IF(COUNTA(E13:E16)=0,"", MIN(E13:E16))</f>
+        <v>45961</v>
       </c>
       <c r="F12" s="11">
-        <f t="shared" ref="F12:F30" si="10">IF(AND(E12&lt;&gt;"", D12&lt;&gt;""), E12+D12-1, "")</f>
-        <v>45961</v>
-      </c>
-      <c r="G12" s="36" t="str" cm="1">
-        <f t="array" ref="G12">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C10:I10="O", 담당자!C$2:I$2, ""))</f>
-        <v>안규태, 장지훈</v>
+        <f>IF(COUNTBLANK(F13:F16)=4,"", MAX(F13:F16))</f>
+        <v>45975</v>
+      </c>
+      <c r="G12" s="38" t="str" cm="1">
+        <f t="array" ref="G12">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C12:I12="O", 담당자!C$2:I$2, ""))</f>
+        <v/>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
@@ -2477,31 +2479,27 @@
     </row>
     <row r="13" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="50"/>
-      <c r="B13" s="41" t="s">
-        <v>28</v>
+      <c r="B13" s="43" t="s">
+        <v>32</v>
       </c>
       <c r="C13" s="37">
-        <f>IF(COUNTBLANK(C14:C17)=4, "", SUM(C14:C17)/COUNT(C14:C17))</f>
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="D13" s="10">
-        <f>IF(AND(F13&lt;&gt;"", E13&lt;&gt;""), F13-E13+1, "")</f>
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E13" s="11">
-        <f>IF(COUNTA(E14:E17)=0,"", MIN(E14:E17))</f>
-        <v>45961</v>
+        <v>45962</v>
       </c>
       <c r="F13" s="11">
-        <f>IF(COUNTBLANK(F14:F17)=4,"", MAX(F14:F17))</f>
-        <v>45975</v>
-      </c>
-      <c r="G13" s="38" t="str" cm="1">
-        <f t="array" ref="G13">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C12:I12="O", 담당자!C$2:I$2, ""))</f>
-        <v/>
+        <f t="shared" si="10"/>
+        <v>45965</v>
+      </c>
+      <c r="G13" s="36" t="str" cm="1">
+        <f t="array" ref="G13">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C13:I13="O", 담당자!C$2:I$2, ""))</f>
+        <v>안규태</v>
       </c>
       <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
       <c r="L13" s="32"/>
@@ -2517,7 +2515,6 @@
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
       <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
       <c r="Z13" s="32"/>
       <c r="AA13" s="33"/>
       <c r="AB13" s="12"/>
@@ -2564,7 +2561,7 @@
     <row r="14" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="50"/>
       <c r="B14" s="43" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="37">
         <v>1</v>
@@ -2580,10 +2577,11 @@
         <v>45965</v>
       </c>
       <c r="G14" s="36" t="str" cm="1">
-        <f t="array" ref="G14">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C13:I13="O", 담당자!C$2:I$2, ""))</f>
-        <v>안규태</v>
+        <f t="array" ref="G14">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C14:I14="O", 담당자!C$2:I$2, ""))</f>
+        <v>안규태, 김수민</v>
       </c>
       <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
       <c r="L14" s="32"/>
@@ -2599,6 +2597,7 @@
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
       <c r="Z14" s="32"/>
       <c r="AA14" s="33"/>
       <c r="AB14" s="12"/>
@@ -2645,24 +2644,24 @@
     <row r="15" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="50"/>
       <c r="B15" s="43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="37">
         <v>1</v>
       </c>
       <c r="D15" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="11">
-        <v>45962</v>
+        <v>45961</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="10"/>
         <v>45965</v>
       </c>
       <c r="G15" s="36" t="str" cm="1">
-        <f t="array" ref="G15">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C14:I14="O", 담당자!C$2:I$2, ""))</f>
-        <v>안규태, 김수민</v>
+        <f t="array" ref="G15">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C15:I15="O", 담당자!C$2:I$2, ""))</f>
+        <v>안규태, 백여랑</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
@@ -2728,24 +2727,24 @@
     <row r="16" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="50"/>
       <c r="B16" s="43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="37">
         <v>1</v>
       </c>
       <c r="D16" s="10">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E16" s="11">
         <v>45961</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="10"/>
-        <v>45965</v>
+        <v>45975</v>
       </c>
       <c r="G16" s="36" t="str" cm="1">
-        <f t="array" ref="G16">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C15:I15="O", 담당자!C$2:I$2, ""))</f>
-        <v>안규태, 백여랑</v>
+        <f t="array" ref="G16">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C16:I16="O", 담당자!C$2:I$2, ""))</f>
+        <v>김수민, 신운용, 장지훈</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
@@ -2810,25 +2809,25 @@
     </row>
     <row r="17" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="50"/>
-      <c r="B17" s="43" t="s">
-        <v>35</v>
+      <c r="B17" s="41" t="s">
+        <v>29</v>
       </c>
       <c r="C17" s="37">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="10">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E17" s="11">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="10"/>
-        <v>45975</v>
+        <v>45965</v>
       </c>
       <c r="G17" s="36" t="str" cm="1">
-        <f t="array" ref="G17">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C16:I16="O", 담당자!C$2:I$2, ""))</f>
-        <v>김수민, 신운용, 장지훈</v>
+        <f t="array" ref="G17">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C17:I17="O", 담당자!C$2:I$2, ""))</f>
+        <v>안규태</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
@@ -2894,24 +2893,27 @@
     <row r="18" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="50"/>
       <c r="B18" s="41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" s="37">
-        <v>0.8</v>
+        <f>IF(COUNTBLANK(C19:C20)=2, "", SUM(C19:C20)/COUNT(C19:C20))</f>
+        <v>1</v>
       </c>
       <c r="D18" s="10">
-        <v>1</v>
+        <f>IF(AND(F18&lt;&gt;"", E18&lt;&gt;""), F18-E18+1, "")</f>
+        <v>31</v>
       </c>
       <c r="E18" s="11">
-        <v>45965</v>
+        <f>IF(COUNTA(E19:E20)=0,"", MIN(E19:E20))</f>
+        <v>45966</v>
       </c>
       <c r="F18" s="11">
-        <f t="shared" si="10"/>
-        <v>45965</v>
-      </c>
-      <c r="G18" s="36" t="str" cm="1">
-        <f t="array" ref="G18">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C17:I17="O", 담당자!C$2:I$2, ""))</f>
-        <v>안규태</v>
+        <f>IF(COUNTBLANK(F19:F20)=2,"", MAX(F19:F20))</f>
+        <v>45996</v>
+      </c>
+      <c r="G18" s="38" t="str" cm="1">
+        <f t="array" ref="G18">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C18:I18="O", 담당자!C$2:I$2, ""))</f>
+        <v/>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
@@ -2976,28 +2978,25 @@
     </row>
     <row r="19" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="50"/>
-      <c r="B19" s="41" t="s">
-        <v>30</v>
+      <c r="B19" s="43" t="s">
+        <v>36</v>
       </c>
       <c r="C19" s="37">
-        <f>IF(COUNTBLANK(C20:C21)=2, "", SUM(C20:C21)/COUNT(C20:C21))</f>
-        <v>0.41500000000000004</v>
+        <v>1</v>
       </c>
       <c r="D19" s="10">
-        <f>IF(AND(F19&lt;&gt;"", E19&lt;&gt;""), F19-E19+1, "")</f>
         <v>31</v>
       </c>
       <c r="E19" s="11">
-        <f>IF(COUNTA(E20:E21)=0,"", MIN(E20:E21))</f>
         <v>45966</v>
       </c>
       <c r="F19" s="11">
-        <f>IF(COUNTBLANK(F20:F21)=2,"", MAX(F20:F21))</f>
+        <f t="shared" si="10"/>
         <v>45996</v>
       </c>
-      <c r="G19" s="38" t="str" cm="1">
-        <f t="array" ref="G19">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C18:I18="O", 담당자!C$2:I$2, ""))</f>
-        <v/>
+      <c r="G19" s="36" t="str" cm="1">
+        <f t="array" ref="G19">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C19:I19="O", 담당자!C$2:I$2, ""))</f>
+        <v>팀 전체</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
@@ -3063,10 +3062,10 @@
     <row r="20" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="50"/>
       <c r="B20" s="43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="37">
-        <v>0.55000000000000004</v>
+        <v>1</v>
       </c>
       <c r="D20" s="10">
         <v>31</v>
@@ -3079,7 +3078,7 @@
         <v>45996</v>
       </c>
       <c r="G20" s="36" t="str" cm="1">
-        <f t="array" ref="G20">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C19:I19="O", 담당자!C$2:I$2, ""))</f>
+        <f t="array" ref="G20">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C20:I20="O", 담당자!C$2:I$2, ""))</f>
         <v>팀 전체</v>
       </c>
       <c r="H20" s="12"/>
@@ -3145,25 +3144,28 @@
     </row>
     <row r="21" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="50"/>
-      <c r="B21" s="43" t="s">
-        <v>37</v>
+      <c r="B21" s="41" t="s">
+        <v>31</v>
       </c>
       <c r="C21" s="37">
-        <v>0.28000000000000003</v>
+        <f>IF(COUNTBLANK(C22:C23)=2, "", SUM(C22:C23)/COUNT(C22:C23))</f>
+        <v>1</v>
       </c>
       <c r="D21" s="10">
-        <v>31</v>
+        <f>IF(AND(F21&lt;&gt;"", E21&lt;&gt;""), F21-E21+1, "")</f>
+        <v>7</v>
       </c>
       <c r="E21" s="11">
-        <v>45966</v>
+        <f>IF(COUNTA(E22:E23)=0,"", MIN(E22:E23))</f>
+        <v>45997</v>
       </c>
       <c r="F21" s="11">
-        <f t="shared" si="10"/>
-        <v>45996</v>
-      </c>
-      <c r="G21" s="36" t="str" cm="1">
-        <f t="array" ref="G21">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C20:I20="O", 담당자!C$2:I$2, ""))</f>
-        <v>팀 전체</v>
+        <f>IF(COUNTBLANK(F22:F23)=2,"", MAX(F22:F23))</f>
+        <v>46003</v>
+      </c>
+      <c r="G21" s="38" t="str" cm="1">
+        <f t="array" ref="G21">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C21:I21="O", 담당자!C$2:I$2, ""))</f>
+        <v/>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
@@ -3228,28 +3230,25 @@
     </row>
     <row r="22" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50"/>
-      <c r="B22" s="41" t="s">
-        <v>31</v>
+      <c r="B22" s="43" t="s">
+        <v>38</v>
       </c>
       <c r="C22" s="37">
-        <f>IF(COUNTBLANK(C23:C24)=2, "", SUM(C23:C24)/COUNT(C23:C24))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="10">
-        <f>IF(AND(F22&lt;&gt;"", E22&lt;&gt;""), F22-E22+1, "")</f>
         <v>7</v>
       </c>
       <c r="E22" s="11">
-        <f>IF(COUNTA(E23:E24)=0,"", MIN(E23:E24))</f>
         <v>45997</v>
       </c>
       <c r="F22" s="11">
-        <f>IF(COUNTBLANK(F23:F24)=2,"", MAX(F23:F24))</f>
+        <f t="shared" si="10"/>
         <v>46003</v>
       </c>
-      <c r="G22" s="38" t="str" cm="1">
-        <f t="array" ref="G22">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C21:I21="O", 담당자!C$2:I$2, ""))</f>
-        <v/>
+      <c r="G22" s="36" t="str" cm="1">
+        <f t="array" ref="G22">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C22:I22="O", 담당자!C$2:I$2, ""))</f>
+        <v>안규태</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
@@ -3315,10 +3314,10 @@
     <row r="23" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="50"/>
       <c r="B23" s="43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="10">
         <v>7</v>
@@ -3331,13 +3330,13 @@
         <v>46003</v>
       </c>
       <c r="G23" s="36" t="str" cm="1">
-        <f t="array" ref="G23">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C22:I22="O", 담당자!C$2:I$2, ""))</f>
-        <v>안규태</v>
+        <f t="array" ref="G23">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C23:I23="O", 담당자!C$2:I$2, ""))</f>
+        <v>팀 전체</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
+      <c r="K23" s="40"/>
       <c r="L23" s="32"/>
       <c r="M23" s="33"/>
       <c r="N23" s="44"/>
@@ -3397,30 +3396,33 @@
     </row>
     <row r="24" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="50"/>
-      <c r="B24" s="43" t="s">
-        <v>39</v>
+      <c r="B24" s="41" t="s">
+        <v>40</v>
       </c>
       <c r="C24" s="37">
-        <v>0</v>
+        <f>IF(COUNTBLANK(C25:C26)=2, "", SUM(C25:C26)/COUNT(C25:C26))</f>
+        <v>1</v>
       </c>
       <c r="D24" s="10">
-        <v>7</v>
+        <f>IF(AND(F24&lt;&gt;"", E24&lt;&gt;""), F24-E24+1, "")</f>
+        <v>4</v>
       </c>
       <c r="E24" s="11">
-        <v>45997</v>
+        <f>IF(COUNTA(E25:E26)=0,"", MIN(E25:E26))</f>
+        <v>46003</v>
       </c>
       <c r="F24" s="11">
-        <f t="shared" si="10"/>
-        <v>46003</v>
-      </c>
-      <c r="G24" s="36" t="str" cm="1">
-        <f t="array" ref="G24">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C23:I23="O", 담당자!C$2:I$2, ""))</f>
-        <v>팀 전체</v>
+        <f>IF(COUNTBLANK(F25:F26)=2,"", MAX(F25:F26))</f>
+        <v>46006</v>
+      </c>
+      <c r="G24" s="38" t="str" cm="1">
+        <f t="array" ref="G24">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C24:I24="O", 담당자!C$2:I$2, ""))</f>
+        <v/>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
-      <c r="K24" s="40"/>
+      <c r="K24" s="12"/>
       <c r="L24" s="32"/>
       <c r="M24" s="33"/>
       <c r="N24" s="44"/>
@@ -3480,28 +3482,25 @@
     </row>
     <row r="25" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="50"/>
-      <c r="B25" s="41" t="s">
-        <v>40</v>
+      <c r="B25" s="43" t="s">
+        <v>41</v>
       </c>
       <c r="C25" s="37">
-        <f>IF(COUNTBLANK(C26:C27)=2, "", SUM(C26:C27)/COUNT(C26:C27))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="10">
-        <f>IF(AND(F25&lt;&gt;"", E25&lt;&gt;""), F25-E25+1, "")</f>
         <v>4</v>
       </c>
       <c r="E25" s="11">
-        <f>IF(COUNTA(E26:E27)=0,"", MIN(E26:E27))</f>
         <v>46003</v>
       </c>
       <c r="F25" s="11">
-        <f>IF(COUNTBLANK(F26:F27)=2,"", MAX(F26:F27))</f>
+        <f t="shared" si="10"/>
         <v>46006</v>
       </c>
-      <c r="G25" s="38" t="str" cm="1">
-        <f t="array" ref="G25">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C24:I24="O", 담당자!C$2:I$2, ""))</f>
-        <v/>
+      <c r="G25" s="36" t="str" cm="1">
+        <f t="array" ref="G25">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C25:I25="O", 담당자!C$2:I$2, ""))</f>
+        <v>팀 전체</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
@@ -3567,10 +3566,10 @@
     <row r="26" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="50"/>
       <c r="B26" s="43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="10">
         <v>4</v>
@@ -3583,7 +3582,7 @@
         <v>46006</v>
       </c>
       <c r="G26" s="36" t="str" cm="1">
-        <f t="array" ref="G26">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C25:I25="O", 담당자!C$2:I$2, ""))</f>
+        <f t="array" ref="G26">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C26:I26="O", 담당자!C$2:I$2, ""))</f>
         <v>팀 전체</v>
       </c>
       <c r="H26" s="12"/>
@@ -3649,25 +3648,28 @@
     </row>
     <row r="27" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="50"/>
-      <c r="B27" s="43" t="s">
-        <v>42</v>
+      <c r="B27" s="41" t="s">
+        <v>47</v>
       </c>
       <c r="C27" s="37">
-        <v>0</v>
+        <f>IF(COUNTBLANK(C28:C29)=2, "", SUM(C28:C29)/COUNT(C28:C29))</f>
+        <v>1</v>
       </c>
       <c r="D27" s="10">
+        <f>IF(AND(F27&lt;&gt;"", E27&lt;&gt;""), F27-E27+1, "")</f>
         <v>4</v>
       </c>
       <c r="E27" s="11">
-        <v>46003</v>
+        <f>IF(COUNTA(E28:E29)=0,"", MIN(E28:E29))</f>
+        <v>46006</v>
       </c>
       <c r="F27" s="11">
-        <f t="shared" si="10"/>
-        <v>46006</v>
-      </c>
-      <c r="G27" s="36" t="str" cm="1">
-        <f t="array" ref="G27">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C26:I26="O", 담당자!C$2:I$2, ""))</f>
-        <v>팀 전체</v>
+        <f>IF(COUNTBLANK(F28:F29)=2,"", MAX(F28:F29))</f>
+        <v>46009</v>
+      </c>
+      <c r="G27" s="38" t="str" cm="1">
+        <f t="array" ref="G27">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C24:I24="O", 담당자!C$2:I$2, ""))</f>
+        <v/>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
@@ -3732,28 +3734,25 @@
     </row>
     <row r="28" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="50"/>
-      <c r="B28" s="41" t="s">
-        <v>47</v>
+      <c r="B28" s="43" t="s">
+        <v>48</v>
       </c>
       <c r="C28" s="37">
-        <f>IF(COUNTBLANK(C29:C30)=2, "", SUM(C29:C30)/COUNT(C29:C30))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="10">
-        <f>IF(AND(F28&lt;&gt;"", E28&lt;&gt;""), F28-E28+1, "")</f>
         <v>4</v>
       </c>
       <c r="E28" s="11">
-        <f>IF(COUNTA(E29:E30)=0,"", MIN(E29:E30))</f>
         <v>46006</v>
       </c>
       <c r="F28" s="11">
-        <f>IF(COUNTBLANK(F29:F30)=2,"", MAX(F29:F30))</f>
+        <f t="shared" si="10"/>
         <v>46009</v>
       </c>
-      <c r="G28" s="38" t="str" cm="1">
-        <f t="array" ref="G28">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C24:I24="O", 담당자!C$2:I$2, ""))</f>
-        <v/>
+      <c r="G28" s="36" t="str" cm="1">
+        <f t="array" ref="G28">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C28:I28="O", 담당자!C$2:I$2, ""))</f>
+        <v>팀 전체</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
@@ -3817,12 +3816,12 @@
       <c r="BO28" s="12"/>
     </row>
     <row r="29" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="50"/>
+      <c r="A29" s="51"/>
       <c r="B29" s="43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C29" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="10">
         <v>4</v>
@@ -3835,7 +3834,7 @@
         <v>46009</v>
       </c>
       <c r="G29" s="36" t="str" cm="1">
-        <f t="array" ref="G29">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C28:I28="O", 담당자!C$2:I$2, ""))</f>
+        <f t="array" ref="G29">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C29:I29="O", 담당자!C$2:I$2, ""))</f>
         <v>팀 전체</v>
       </c>
       <c r="H29" s="12"/>
@@ -3900,258 +3899,68 @@
       <c r="BO29" s="12"/>
     </row>
     <row r="30" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="50"/>
-      <c r="B30" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="37">
-        <v>0</v>
-      </c>
-      <c r="D30" s="10">
-        <v>4</v>
-      </c>
-      <c r="E30" s="11">
-        <v>46006</v>
-      </c>
-      <c r="F30" s="11">
-        <f t="shared" si="10"/>
-        <v>46009</v>
-      </c>
-      <c r="G30" s="36" t="str" cm="1">
-        <f t="array" ref="G30">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C29:I29="O", 담당자!C$2:I$2, ""))</f>
-        <v>팀 전체</v>
-      </c>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="47"/>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="32"/>
-      <c r="T30" s="33"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="32"/>
-      <c r="AA30" s="33"/>
-      <c r="AB30" s="12"/>
-      <c r="AC30" s="12"/>
-      <c r="AD30" s="12"/>
-      <c r="AE30" s="12"/>
-      <c r="AF30" s="12"/>
-      <c r="AG30" s="32"/>
-      <c r="AH30" s="33"/>
-      <c r="AI30" s="12"/>
-      <c r="AJ30" s="12"/>
-      <c r="AK30" s="12"/>
-      <c r="AL30" s="12"/>
-      <c r="AM30" s="12"/>
-      <c r="AN30" s="32"/>
-      <c r="AO30" s="33"/>
-      <c r="AP30" s="12"/>
-      <c r="AQ30" s="12"/>
-      <c r="AR30" s="12"/>
-      <c r="AS30" s="12"/>
-      <c r="AT30" s="12"/>
-      <c r="AU30" s="32"/>
-      <c r="AV30" s="33"/>
-      <c r="AW30" s="12"/>
-      <c r="AX30" s="12"/>
-      <c r="AY30" s="12"/>
-      <c r="AZ30" s="12"/>
-      <c r="BA30" s="12"/>
-      <c r="BB30" s="32"/>
-      <c r="BC30" s="33"/>
-      <c r="BD30" s="12"/>
-      <c r="BE30" s="12"/>
-      <c r="BF30" s="12"/>
-      <c r="BG30" s="12"/>
-      <c r="BH30" s="12"/>
-      <c r="BI30" s="32"/>
-      <c r="BJ30" s="33"/>
-      <c r="BK30" s="12"/>
-      <c r="BL30" s="12"/>
-      <c r="BM30" s="12"/>
-      <c r="BN30" s="12"/>
-      <c r="BO30" s="12"/>
-    </row>
-    <row r="31" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="50"/>
-      <c r="B31" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="37">
-        <f>IF(COUNTBLANK(C32:C32)=2, "", SUM(C32:C32)/COUNT(C32:C32))</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="10">
-        <f>IF(AND(F31&lt;&gt;"", E31&lt;&gt;""), F31-E31+1, "")</f>
-        <v>2</v>
-      </c>
-      <c r="E31" s="11">
-        <f>IF(COUNTA(E32:E32)=0,"", MIN(E32:E32))</f>
-        <v>45958</v>
-      </c>
-      <c r="F31" s="11">
-        <f>IF(COUNTBLANK(F32:F32)=2,"", MAX(F32:F32))</f>
-        <v>45959</v>
-      </c>
-      <c r="G31" s="38" t="str" cm="1">
-        <f t="array" ref="G31">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C27:I27="O", 담당자!C$2:I$2, ""))</f>
-        <v/>
-      </c>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="33"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="47"/>
-      <c r="P31" s="47"/>
-      <c r="Q31" s="45"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="32"/>
-      <c r="T31" s="33"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="12"/>
-      <c r="W31" s="12"/>
-      <c r="X31" s="12"/>
-      <c r="Y31" s="12"/>
-      <c r="Z31" s="32"/>
-      <c r="AA31" s="33"/>
-      <c r="AB31" s="12"/>
-      <c r="AC31" s="12"/>
-      <c r="AD31" s="12"/>
-      <c r="AE31" s="12"/>
-      <c r="AF31" s="12"/>
-      <c r="AG31" s="32"/>
-      <c r="AH31" s="33"/>
-      <c r="AI31" s="12"/>
-      <c r="AJ31" s="12"/>
-      <c r="AK31" s="12"/>
-      <c r="AL31" s="12"/>
-      <c r="AM31" s="12"/>
-      <c r="AN31" s="32"/>
-      <c r="AO31" s="33"/>
-      <c r="AP31" s="12"/>
-      <c r="AQ31" s="12"/>
-      <c r="AR31" s="12"/>
-      <c r="AS31" s="12"/>
-      <c r="AT31" s="12"/>
-      <c r="AU31" s="32"/>
-      <c r="AV31" s="33"/>
-      <c r="AW31" s="12"/>
-      <c r="AX31" s="12"/>
-      <c r="AY31" s="12"/>
-      <c r="AZ31" s="12"/>
-      <c r="BA31" s="12"/>
-      <c r="BB31" s="32"/>
-      <c r="BC31" s="33"/>
-      <c r="BD31" s="12"/>
-      <c r="BE31" s="12"/>
-      <c r="BF31" s="12"/>
-      <c r="BG31" s="12"/>
-      <c r="BH31" s="12"/>
-      <c r="BI31" s="32"/>
-      <c r="BJ31" s="33"/>
-      <c r="BK31" s="12"/>
-      <c r="BL31" s="12"/>
-      <c r="BM31" s="12"/>
-      <c r="BN31" s="12"/>
-      <c r="BO31" s="12"/>
-    </row>
-    <row r="32" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="51"/>
-      <c r="B32" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="37">
-        <v>0</v>
-      </c>
-      <c r="D32" s="10">
-        <v>2</v>
-      </c>
-      <c r="E32" s="11">
-        <v>45958</v>
-      </c>
-      <c r="F32" s="11">
-        <f t="shared" ref="F32" si="11">IF(AND(E32&lt;&gt;"", D32&lt;&gt;""), E32+D32-1, "")</f>
-        <v>45959</v>
-      </c>
-      <c r="G32" s="36" t="str" cm="1">
-        <f t="array" ref="G32">_xlfn.TEXTJOIN(", ", TRUE, IF(담당자!C28:I28="O", 담당자!C$2:I$2, ""))</f>
-        <v>팀 전체</v>
-      </c>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="32"/>
-      <c r="M32" s="33"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="47"/>
-      <c r="P32" s="47"/>
-      <c r="Q32" s="45"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="32"/>
-      <c r="T32" s="33"/>
-      <c r="U32" s="12"/>
-      <c r="V32" s="12"/>
-      <c r="W32" s="12"/>
-      <c r="X32" s="12"/>
-      <c r="Y32" s="12"/>
-      <c r="Z32" s="32"/>
-      <c r="AA32" s="33"/>
-      <c r="AB32" s="12"/>
-      <c r="AC32" s="12"/>
-      <c r="AD32" s="12"/>
-      <c r="AE32" s="12"/>
-      <c r="AF32" s="12"/>
-      <c r="AG32" s="32"/>
-      <c r="AH32" s="33"/>
-      <c r="AI32" s="12"/>
-      <c r="AJ32" s="12"/>
-      <c r="AK32" s="12"/>
-      <c r="AL32" s="12"/>
-      <c r="AM32" s="12"/>
-      <c r="AN32" s="32"/>
-      <c r="AO32" s="33"/>
-      <c r="AP32" s="12"/>
-      <c r="AQ32" s="12"/>
-      <c r="AR32" s="12"/>
-      <c r="AS32" s="12"/>
-      <c r="AT32" s="12"/>
-      <c r="AU32" s="32"/>
-      <c r="AV32" s="33"/>
-      <c r="AW32" s="12"/>
-      <c r="AX32" s="12"/>
-      <c r="AY32" s="12"/>
-      <c r="AZ32" s="12"/>
-      <c r="BA32" s="12"/>
-      <c r="BB32" s="32"/>
-      <c r="BC32" s="33"/>
-      <c r="BD32" s="12"/>
-      <c r="BE32" s="12"/>
-      <c r="BF32" s="12"/>
-      <c r="BG32" s="12"/>
-      <c r="BH32" s="12"/>
-      <c r="BI32" s="32"/>
-      <c r="BJ32" s="33"/>
-      <c r="BK32" s="12"/>
-      <c r="BL32" s="12"/>
-      <c r="BM32" s="12"/>
-      <c r="BN32" s="12"/>
-      <c r="BO32" s="12"/>
-    </row>
-    <row r="33" spans="5:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="26"/>
+      <c r="U30" s="13"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+    </row>
+    <row r="31" spans="1:67" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="22"/>
+      <c r="T31" s="26"/>
+      <c r="U31" s="13"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="13"/>
+    </row>
+    <row r="32" spans="1:67" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="13"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="13"/>
+    </row>
+    <row r="33" spans="5:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E33" s="14"/>
       <c r="F33" s="14"/>
       <c r="H33" s="13"/>
@@ -4161,10 +3970,8 @@
       <c r="L33" s="22"/>
       <c r="M33" s="26"/>
       <c r="N33" s="13"/>
-      <c r="O33" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="P33" s="48"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
       <c r="R33" s="13"/>
       <c r="S33" s="22"/>
@@ -4173,65 +3980,17 @@
       <c r="V33" s="13"/>
       <c r="W33" s="13"/>
     </row>
-    <row r="34" spans="5:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="13"/>
-      <c r="Q34" s="13"/>
-      <c r="R34" s="13"/>
-      <c r="S34" s="22"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="13"/>
-      <c r="V34" s="13"/>
-      <c r="W34" s="13"/>
-    </row>
-    <row r="35" spans="5:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
-      <c r="S35" s="22"/>
-      <c r="T35" s="26"/>
-      <c r="U35" s="13"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="13"/>
-    </row>
-    <row r="36" spans="5:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="13"/>
-      <c r="Q36" s="13"/>
-      <c r="R36" s="13"/>
-      <c r="S36" s="22"/>
-      <c r="T36" s="26"/>
-      <c r="U36" s="13"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="13"/>
+    <row r="34" spans="5:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+    </row>
+    <row r="35" spans="5:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+    </row>
+    <row r="36" spans="5:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
     </row>
     <row r="37" spans="5:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E37" s="15"/>
@@ -8081,23 +7840,11 @@
       <c r="E998" s="15"/>
       <c r="F998" s="15"/>
     </row>
-    <row r="999" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E999" s="15"/>
-      <c r="F999" s="15"/>
-    </row>
-    <row r="1000" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E1000" s="15"/>
-      <c r="F1000" s="15"/>
-    </row>
-    <row r="1001" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E1001" s="15"/>
-      <c r="F1001" s="15"/>
-    </row>
   </sheetData>
   <autoFilter ref="A3:F4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="12">
-    <mergeCell ref="A9:A32"/>
-    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A8:A29"/>
+    <mergeCell ref="A5:A7"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="A1:W1"/>
@@ -8110,27 +7857,22 @@
     <mergeCell ref="D3:D4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="H5:BO8 H10:BO12 H14:BO18 H20:BO21 H23:BO24 H26:BO27 H29:BO30">
-    <cfRule type="expression" dxfId="4" priority="8">
+  <conditionalFormatting sqref="H5:BO7 H9:BO11 H13:BO17 H19:BO20 H22:BO23 H25:BO26 H28:BO29">
+    <cfRule type="expression" dxfId="3" priority="8">
       <formula>AND(AND($E5&lt;&gt;"", $F5&lt;&gt;""), AND(H$4&gt;=$E5, H$4&lt;=$F5))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:BO32">
-    <cfRule type="expression" dxfId="3" priority="10">
+  <conditionalFormatting sqref="H5:BO29">
+    <cfRule type="expression" dxfId="2" priority="10">
       <formula>AND(H$4&lt;&gt;"",WEEKDAY(H$4)=1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="12">
+    <cfRule type="expression" dxfId="1" priority="12">
       <formula>AND(H$4&lt;&gt;"", WEEKDAY(H$4)=7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H9:BO9 H13:BO13 H19:BO19 H22:BO22 H25:BO25 H28:BO28 BO31">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND(AND($E9&lt;&gt;"", $F9&lt;&gt;""), AND(H$4&gt;=$E9, H$4&lt;=$F9))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32:BO32">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(AND($E32&lt;&gt;"", $F32&lt;&gt;""), AND(H$4&gt;=$E32, H$4&lt;=$F32))</formula>
+  <conditionalFormatting sqref="H8:BO8 H12:BO12 H18:BO18 H21:BO21 H24:BO24 H27:BO27">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>AND(AND($E8&lt;&gt;"", $F8&lt;&gt;""), AND(H$4&gt;=$E8, H$4&lt;=$F8))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -8140,8 +7882,8 @@
     <oddFooter>&amp;C&amp;P/</oddFooter>
   </headerFooter>
   <ignoredErrors>
-    <ignoredError sqref="F9 F13 F25 F22 F19 F28 F31" formula="1"/>
-    <ignoredError sqref="E13 C13" formulaRange="1"/>
+    <ignoredError sqref="F8 F12 F24 F21 F18 F27" formula="1"/>
+    <ignoredError sqref="E12 C12" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8210,22 +7952,22 @@
       <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="55"/>
-      <c r="B2" s="66"/>
+      <c r="B2" s="69"/>
       <c r="C2" s="34" t="s">
         <v>44</v>
       </c>
@@ -8315,13 +8057,13 @@
       <c r="B7" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="70"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="67"/>
     </row>
     <row r="8" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="50"/>
@@ -8394,13 +8136,13 @@
       <c r="B12" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="70"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="67"/>
     </row>
     <row r="13" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="50"/>
@@ -8490,13 +8232,13 @@
       <c r="B18" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="70"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="67"/>
     </row>
     <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="50"/>
@@ -8533,13 +8275,13 @@
       <c r="B21" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="70"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="67"/>
     </row>
     <row r="22" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50"/>
@@ -8576,13 +8318,13 @@
       <c r="B24" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="68"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="70"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="67"/>
     </row>
     <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="50"/>
@@ -8619,13 +8361,13 @@
       <c r="B27" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="68"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="70"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="67"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="50"/>
@@ -8662,13 +8404,13 @@
       <c r="B30" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="70"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="67"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="50"/>
@@ -8702,6 +8444,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C7:I7"/>
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="C12:I12"/>
@@ -8709,11 +8456,6 @@
     <mergeCell ref="A7:A32"/>
     <mergeCell ref="C27:I27"/>
     <mergeCell ref="C30:I30"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C7:I7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
